--- a/artfynd/A 45158-2023 artfynd.xlsx
+++ b/artfynd/A 45158-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113470425</v>
+        <v>113470423</v>
       </c>
       <c r="B2" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452327</v>
+        <v>452279</v>
       </c>
       <c r="R2" t="n">
-        <v>6506467</v>
+        <v>6506506</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113470377</v>
+        <v>113470376</v>
       </c>
       <c r="B3" t="n">
-        <v>56781</v>
+        <v>97326</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,40 +789,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452323</v>
+        <v>452378</v>
       </c>
       <c r="R3" t="n">
         <v>6506464</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113470429</v>
+        <v>113470425</v>
       </c>
       <c r="B4" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452529</v>
+        <v>452327</v>
       </c>
       <c r="R4" t="n">
-        <v>6506432</v>
+        <v>6506467</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +984,7 @@
         <v>113470378</v>
       </c>
       <c r="B5" t="n">
-        <v>97314</v>
+        <v>97326</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113470421</v>
+        <v>113470427</v>
       </c>
       <c r="B6" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452247</v>
+        <v>452388</v>
       </c>
       <c r="R6" t="n">
-        <v>6506489</v>
+        <v>6506449</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113470423</v>
+        <v>113470377</v>
       </c>
       <c r="B7" t="n">
-        <v>78121</v>
+        <v>56782</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,34 +1201,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452279</v>
+        <v>452323</v>
       </c>
       <c r="R7" t="n">
-        <v>6506506</v>
+        <v>6506464</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113470431</v>
+        <v>113470421</v>
       </c>
       <c r="B8" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452564</v>
+        <v>452247</v>
       </c>
       <c r="R8" t="n">
-        <v>6506405</v>
+        <v>6506489</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113470427</v>
+        <v>113470429</v>
       </c>
       <c r="B9" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452388</v>
+        <v>452529</v>
       </c>
       <c r="R9" t="n">
-        <v>6506449</v>
+        <v>6506432</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113470376</v>
+        <v>113470431</v>
       </c>
       <c r="B10" t="n">
-        <v>97314</v>
+        <v>78133</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452378</v>
+        <v>452564</v>
       </c>
       <c r="R10" t="n">
-        <v>6506464</v>
+        <v>6506405</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45158-2023 artfynd.xlsx
+++ b/artfynd/A 45158-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113470423</v>
+        <v>113470378</v>
       </c>
       <c r="B2" t="n">
-        <v>78133</v>
+        <v>97326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452279</v>
+        <v>452483</v>
       </c>
       <c r="R2" t="n">
-        <v>6506506</v>
+        <v>6506438</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113470376</v>
+        <v>113470429</v>
       </c>
       <c r="B3" t="n">
-        <v>97326</v>
+        <v>78133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452378</v>
+        <v>452529</v>
       </c>
       <c r="R3" t="n">
-        <v>6506464</v>
+        <v>6506432</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113470425</v>
+        <v>113470377</v>
       </c>
       <c r="B4" t="n">
-        <v>78133</v>
+        <v>56782</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452327</v>
+        <v>452323</v>
       </c>
       <c r="R4" t="n">
-        <v>6506467</v>
+        <v>6506464</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113470378</v>
+        <v>113470427</v>
       </c>
       <c r="B5" t="n">
-        <v>97326</v>
+        <v>78133</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452483</v>
+        <v>452388</v>
       </c>
       <c r="R5" t="n">
-        <v>6506438</v>
+        <v>6506449</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113470427</v>
+        <v>113470431</v>
       </c>
       <c r="B6" t="n">
         <v>78133</v>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452388</v>
+        <v>452564</v>
       </c>
       <c r="R6" t="n">
-        <v>6506449</v>
+        <v>6506405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113470377</v>
+        <v>113470425</v>
       </c>
       <c r="B7" t="n">
-        <v>56782</v>
+        <v>78133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,39 +1206,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452323</v>
+        <v>452327</v>
       </c>
       <c r="R7" t="n">
-        <v>6506464</v>
+        <v>6506467</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113470421</v>
+        <v>113470423</v>
       </c>
       <c r="B8" t="n">
         <v>78133</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452247</v>
+        <v>452279</v>
       </c>
       <c r="R8" t="n">
-        <v>6506489</v>
+        <v>6506506</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113470429</v>
+        <v>113470376</v>
       </c>
       <c r="B9" t="n">
-        <v>78133</v>
+        <v>97326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452529</v>
+        <v>452378</v>
       </c>
       <c r="R9" t="n">
-        <v>6506432</v>
+        <v>6506464</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113470431</v>
+        <v>113470421</v>
       </c>
       <c r="B10" t="n">
         <v>78133</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452564</v>
+        <v>452247</v>
       </c>
       <c r="R10" t="n">
-        <v>6506405</v>
+        <v>6506489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45158-2023 artfynd.xlsx
+++ b/artfynd/A 45158-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113470378</v>
+        <v>113470376</v>
       </c>
       <c r="B2" t="n">
-        <v>97326</v>
+        <v>97348</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452483</v>
+        <v>452378</v>
       </c>
       <c r="R2" t="n">
-        <v>6506438</v>
+        <v>6506464</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113470429</v>
+        <v>113470431</v>
       </c>
       <c r="B3" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452529</v>
+        <v>452564</v>
       </c>
       <c r="R3" t="n">
-        <v>6506432</v>
+        <v>6506405</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113470377</v>
+        <v>113470427</v>
       </c>
       <c r="B4" t="n">
-        <v>56782</v>
+        <v>78155</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,39 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452323</v>
+        <v>452388</v>
       </c>
       <c r="R4" t="n">
-        <v>6506464</v>
+        <v>6506449</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113470427</v>
+        <v>113470425</v>
       </c>
       <c r="B5" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452388</v>
+        <v>452327</v>
       </c>
       <c r="R5" t="n">
-        <v>6506449</v>
+        <v>6506467</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113470431</v>
+        <v>113470429</v>
       </c>
       <c r="B6" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452564</v>
+        <v>452529</v>
       </c>
       <c r="R6" t="n">
-        <v>6506405</v>
+        <v>6506432</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113470425</v>
+        <v>113470377</v>
       </c>
       <c r="B7" t="n">
-        <v>78133</v>
+        <v>56782</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,34 +1201,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452327</v>
+        <v>452323</v>
       </c>
       <c r="R7" t="n">
-        <v>6506467</v>
+        <v>6506464</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113470423</v>
+        <v>113470378</v>
       </c>
       <c r="B8" t="n">
-        <v>78133</v>
+        <v>97348</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452279</v>
+        <v>452483</v>
       </c>
       <c r="R8" t="n">
-        <v>6506506</v>
+        <v>6506438</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113470376</v>
+        <v>113470421</v>
       </c>
       <c r="B9" t="n">
-        <v>97326</v>
+        <v>78155</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452378</v>
+        <v>452247</v>
       </c>
       <c r="R9" t="n">
-        <v>6506464</v>
+        <v>6506489</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113470421</v>
+        <v>113470423</v>
       </c>
       <c r="B10" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452247</v>
+        <v>452279</v>
       </c>
       <c r="R10" t="n">
-        <v>6506489</v>
+        <v>6506506</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45158-2023 artfynd.xlsx
+++ b/artfynd/A 45158-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113470376</v>
+        <v>113470425</v>
       </c>
       <c r="B2" t="n">
-        <v>97348</v>
+        <v>78158</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452378</v>
+        <v>452327</v>
       </c>
       <c r="R2" t="n">
-        <v>6506464</v>
+        <v>6506467</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113470431</v>
+        <v>113470376</v>
       </c>
       <c r="B3" t="n">
-        <v>78155</v>
+        <v>97352</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452564</v>
+        <v>452378</v>
       </c>
       <c r="R3" t="n">
-        <v>6506405</v>
+        <v>6506464</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113470427</v>
+        <v>113470378</v>
       </c>
       <c r="B4" t="n">
-        <v>78155</v>
+        <v>97352</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452388</v>
+        <v>452483</v>
       </c>
       <c r="R4" t="n">
-        <v>6506449</v>
+        <v>6506438</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113470425</v>
+        <v>113470429</v>
       </c>
       <c r="B5" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452327</v>
+        <v>452529</v>
       </c>
       <c r="R5" t="n">
-        <v>6506467</v>
+        <v>6506432</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113470429</v>
+        <v>113470431</v>
       </c>
       <c r="B6" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452529</v>
+        <v>452564</v>
       </c>
       <c r="R6" t="n">
-        <v>6506432</v>
+        <v>6506405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113470377</v>
+        <v>113470423</v>
       </c>
       <c r="B7" t="n">
-        <v>56782</v>
+        <v>78158</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,39 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452323</v>
+        <v>452279</v>
       </c>
       <c r="R7" t="n">
-        <v>6506464</v>
+        <v>6506506</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113470378</v>
+        <v>113470377</v>
       </c>
       <c r="B8" t="n">
-        <v>97348</v>
+        <v>56785</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,38 +1299,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452483</v>
+        <v>452323</v>
       </c>
       <c r="R8" t="n">
-        <v>6506438</v>
+        <v>6506464</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113470421</v>
+        <v>113470427</v>
       </c>
       <c r="B9" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452247</v>
+        <v>452388</v>
       </c>
       <c r="R9" t="n">
-        <v>6506489</v>
+        <v>6506449</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113470423</v>
+        <v>113470421</v>
       </c>
       <c r="B10" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452279</v>
+        <v>452247</v>
       </c>
       <c r="R10" t="n">
-        <v>6506506</v>
+        <v>6506489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45158-2023 artfynd.xlsx
+++ b/artfynd/A 45158-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113470425</v>
+        <v>113470429</v>
       </c>
       <c r="B2" t="n">
         <v>78158</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452327</v>
+        <v>452529</v>
       </c>
       <c r="R2" t="n">
-        <v>6506467</v>
+        <v>6506432</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113470376</v>
+        <v>113470377</v>
       </c>
       <c r="B3" t="n">
-        <v>97352</v>
+        <v>56785</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,35 +789,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452378</v>
+        <v>452323</v>
       </c>
       <c r="R3" t="n">
         <v>6506464</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113470378</v>
+        <v>113470421</v>
       </c>
       <c r="B4" t="n">
-        <v>97352</v>
+        <v>78158</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452483</v>
+        <v>452247</v>
       </c>
       <c r="R4" t="n">
-        <v>6506438</v>
+        <v>6506489</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113470429</v>
+        <v>113470425</v>
       </c>
       <c r="B5" t="n">
         <v>78158</v>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452529</v>
+        <v>452327</v>
       </c>
       <c r="R5" t="n">
-        <v>6506432</v>
+        <v>6506467</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113470431</v>
+        <v>113470378</v>
       </c>
       <c r="B6" t="n">
-        <v>78158</v>
+        <v>97352</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452564</v>
+        <v>452483</v>
       </c>
       <c r="R6" t="n">
-        <v>6506405</v>
+        <v>6506438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113470377</v>
+        <v>113470427</v>
       </c>
       <c r="B8" t="n">
-        <v>56785</v>
+        <v>78158</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,39 +1308,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452323</v>
+        <v>452388</v>
       </c>
       <c r="R8" t="n">
-        <v>6506464</v>
+        <v>6506449</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113470427</v>
+        <v>113470376</v>
       </c>
       <c r="B9" t="n">
-        <v>78158</v>
+        <v>97352</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452388</v>
+        <v>452378</v>
       </c>
       <c r="R9" t="n">
-        <v>6506449</v>
+        <v>6506464</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113470421</v>
+        <v>113470431</v>
       </c>
       <c r="B10" t="n">
         <v>78158</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452247</v>
+        <v>452564</v>
       </c>
       <c r="R10" t="n">
-        <v>6506489</v>
+        <v>6506405</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45158-2023 artfynd.xlsx
+++ b/artfynd/A 45158-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113470429</v>
+        <v>113470378</v>
       </c>
       <c r="B2" t="n">
-        <v>78158</v>
+        <v>97358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452529</v>
+        <v>452483</v>
       </c>
       <c r="R2" t="n">
-        <v>6506432</v>
+        <v>6506438</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113470377</v>
+        <v>113470425</v>
       </c>
       <c r="B3" t="n">
-        <v>56785</v>
+        <v>78164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452323</v>
+        <v>452327</v>
       </c>
       <c r="R3" t="n">
-        <v>6506464</v>
+        <v>6506467</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +882,7 @@
         <v>113470421</v>
       </c>
       <c r="B4" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113470425</v>
+        <v>113470427</v>
       </c>
       <c r="B5" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452327</v>
+        <v>452388</v>
       </c>
       <c r="R5" t="n">
-        <v>6506467</v>
+        <v>6506449</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113470378</v>
+        <v>113470429</v>
       </c>
       <c r="B6" t="n">
-        <v>97352</v>
+        <v>78164</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452483</v>
+        <v>452529</v>
       </c>
       <c r="R6" t="n">
-        <v>6506438</v>
+        <v>6506432</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113470423</v>
+        <v>113470431</v>
       </c>
       <c r="B7" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452279</v>
+        <v>452564</v>
       </c>
       <c r="R7" t="n">
-        <v>6506506</v>
+        <v>6506405</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113470427</v>
+        <v>113470376</v>
       </c>
       <c r="B8" t="n">
-        <v>78158</v>
+        <v>97358</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452388</v>
+        <v>452378</v>
       </c>
       <c r="R8" t="n">
-        <v>6506449</v>
+        <v>6506464</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113470376</v>
+        <v>113470423</v>
       </c>
       <c r="B9" t="n">
-        <v>97352</v>
+        <v>78164</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452378</v>
+        <v>452279</v>
       </c>
       <c r="R9" t="n">
-        <v>6506464</v>
+        <v>6506506</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113470431</v>
+        <v>113470377</v>
       </c>
       <c r="B10" t="n">
-        <v>78158</v>
+        <v>56789</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,34 +1507,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452564</v>
+        <v>452323</v>
       </c>
       <c r="R10" t="n">
-        <v>6506405</v>
+        <v>6506464</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45158-2023 artfynd.xlsx
+++ b/artfynd/A 45158-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113470378</v>
+        <v>113470425</v>
       </c>
       <c r="B2" t="n">
-        <v>97358</v>
+        <v>78164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452483</v>
+        <v>452327</v>
       </c>
       <c r="R2" t="n">
-        <v>6506438</v>
+        <v>6506467</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113470425</v>
+        <v>113470421</v>
       </c>
       <c r="B3" t="n">
         <v>78164</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452327</v>
+        <v>452247</v>
       </c>
       <c r="R3" t="n">
-        <v>6506467</v>
+        <v>6506489</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113470421</v>
+        <v>113470423</v>
       </c>
       <c r="B4" t="n">
         <v>78164</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452247</v>
+        <v>452279</v>
       </c>
       <c r="R4" t="n">
-        <v>6506489</v>
+        <v>6506506</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113470427</v>
+        <v>113470431</v>
       </c>
       <c r="B5" t="n">
         <v>78164</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452388</v>
+        <v>452564</v>
       </c>
       <c r="R5" t="n">
-        <v>6506449</v>
+        <v>6506405</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113470429</v>
+        <v>113470376</v>
       </c>
       <c r="B6" t="n">
-        <v>78164</v>
+        <v>97358</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452529</v>
+        <v>452378</v>
       </c>
       <c r="R6" t="n">
-        <v>6506432</v>
+        <v>6506464</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113470431</v>
+        <v>113470378</v>
       </c>
       <c r="B7" t="n">
-        <v>78164</v>
+        <v>97358</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452564</v>
+        <v>452483</v>
       </c>
       <c r="R7" t="n">
-        <v>6506405</v>
+        <v>6506438</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113470376</v>
+        <v>113470377</v>
       </c>
       <c r="B8" t="n">
-        <v>97358</v>
+        <v>56789</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,35 +1299,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452378</v>
+        <v>452323</v>
       </c>
       <c r="R8" t="n">
         <v>6506464</v>
@@ -1389,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113470423</v>
+        <v>113470429</v>
       </c>
       <c r="B9" t="n">
         <v>78164</v>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452279</v>
+        <v>452529</v>
       </c>
       <c r="R9" t="n">
-        <v>6506506</v>
+        <v>6506432</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113470377</v>
+        <v>113470427</v>
       </c>
       <c r="B10" t="n">
-        <v>56789</v>
+        <v>78164</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,39 +1512,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452323</v>
+        <v>452388</v>
       </c>
       <c r="R10" t="n">
-        <v>6506464</v>
+        <v>6506449</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45158-2023 artfynd.xlsx
+++ b/artfynd/A 45158-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113470425</v>
+        <v>113470421</v>
       </c>
       <c r="B2" t="n">
-        <v>78164</v>
+        <v>78171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452327</v>
+        <v>452247</v>
       </c>
       <c r="R2" t="n">
-        <v>6506467</v>
+        <v>6506489</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113470421</v>
+        <v>113470376</v>
       </c>
       <c r="B3" t="n">
-        <v>78164</v>
+        <v>97365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452247</v>
+        <v>452378</v>
       </c>
       <c r="R3" t="n">
-        <v>6506489</v>
+        <v>6506464</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113470423</v>
+        <v>113470378</v>
       </c>
       <c r="B4" t="n">
-        <v>78164</v>
+        <v>97365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452279</v>
+        <v>452483</v>
       </c>
       <c r="R4" t="n">
-        <v>6506506</v>
+        <v>6506438</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113470431</v>
+        <v>113470427</v>
       </c>
       <c r="B5" t="n">
-        <v>78164</v>
+        <v>78171</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452564</v>
+        <v>452388</v>
       </c>
       <c r="R5" t="n">
-        <v>6506405</v>
+        <v>6506449</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113470376</v>
+        <v>113470377</v>
       </c>
       <c r="B6" t="n">
-        <v>97358</v>
+        <v>56796</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,35 +1095,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452378</v>
+        <v>452323</v>
       </c>
       <c r="R6" t="n">
         <v>6506464</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113470378</v>
+        <v>113470429</v>
       </c>
       <c r="B7" t="n">
-        <v>97358</v>
+        <v>78171</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452483</v>
+        <v>452529</v>
       </c>
       <c r="R7" t="n">
-        <v>6506438</v>
+        <v>6506432</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113470377</v>
+        <v>113470431</v>
       </c>
       <c r="B8" t="n">
-        <v>56789</v>
+        <v>78171</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,39 +1308,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452323</v>
+        <v>452564</v>
       </c>
       <c r="R8" t="n">
-        <v>6506464</v>
+        <v>6506405</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113470429</v>
+        <v>113470425</v>
       </c>
       <c r="B9" t="n">
-        <v>78164</v>
+        <v>78171</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452529</v>
+        <v>452327</v>
       </c>
       <c r="R9" t="n">
-        <v>6506432</v>
+        <v>6506467</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113470427</v>
+        <v>113470423</v>
       </c>
       <c r="B10" t="n">
-        <v>78164</v>
+        <v>78171</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452388</v>
+        <v>452279</v>
       </c>
       <c r="R10" t="n">
-        <v>6506449</v>
+        <v>6506506</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45158-2023 artfynd.xlsx
+++ b/artfynd/A 45158-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113470421</v>
+        <v>113470423</v>
       </c>
       <c r="B2" t="n">
-        <v>78171</v>
+        <v>78173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452247</v>
+        <v>452279</v>
       </c>
       <c r="R2" t="n">
-        <v>6506489</v>
+        <v>6506506</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113470376</v>
+        <v>113470431</v>
       </c>
       <c r="B3" t="n">
-        <v>97365</v>
+        <v>78173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452378</v>
+        <v>452564</v>
       </c>
       <c r="R3" t="n">
-        <v>6506464</v>
+        <v>6506405</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113470378</v>
+        <v>113470421</v>
       </c>
       <c r="B4" t="n">
-        <v>97365</v>
+        <v>78173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452483</v>
+        <v>452247</v>
       </c>
       <c r="R4" t="n">
-        <v>6506438</v>
+        <v>6506489</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113470427</v>
+        <v>113470378</v>
       </c>
       <c r="B5" t="n">
-        <v>78171</v>
+        <v>97370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452388</v>
+        <v>452483</v>
       </c>
       <c r="R5" t="n">
-        <v>6506449</v>
+        <v>6506438</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113470377</v>
+        <v>113470429</v>
       </c>
       <c r="B6" t="n">
-        <v>56796</v>
+        <v>78173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,39 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452323</v>
+        <v>452529</v>
       </c>
       <c r="R6" t="n">
-        <v>6506464</v>
+        <v>6506432</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113470429</v>
+        <v>113470427</v>
       </c>
       <c r="B7" t="n">
-        <v>78171</v>
+        <v>78173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452529</v>
+        <v>452388</v>
       </c>
       <c r="R7" t="n">
-        <v>6506432</v>
+        <v>6506449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113470431</v>
+        <v>113470425</v>
       </c>
       <c r="B8" t="n">
-        <v>78171</v>
+        <v>78173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452564</v>
+        <v>452327</v>
       </c>
       <c r="R8" t="n">
-        <v>6506405</v>
+        <v>6506467</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113470425</v>
+        <v>113470376</v>
       </c>
       <c r="B9" t="n">
-        <v>78171</v>
+        <v>97370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452327</v>
+        <v>452378</v>
       </c>
       <c r="R9" t="n">
-        <v>6506467</v>
+        <v>6506464</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113470423</v>
+        <v>113470377</v>
       </c>
       <c r="B10" t="n">
-        <v>78171</v>
+        <v>56798</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,34 +1507,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452279</v>
+        <v>452323</v>
       </c>
       <c r="R10" t="n">
-        <v>6506506</v>
+        <v>6506464</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45158-2023 artfynd.xlsx
+++ b/artfynd/A 45158-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113470423</v>
+        <v>113470425</v>
       </c>
       <c r="B2" t="n">
-        <v>78173</v>
+        <v>78201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452279</v>
+        <v>452327</v>
       </c>
       <c r="R2" t="n">
-        <v>6506506</v>
+        <v>6506467</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>113470431</v>
       </c>
       <c r="B3" t="n">
-        <v>78173</v>
+        <v>78201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113470421</v>
+        <v>113470429</v>
       </c>
       <c r="B4" t="n">
-        <v>78173</v>
+        <v>78201</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452247</v>
+        <v>452529</v>
       </c>
       <c r="R4" t="n">
-        <v>6506489</v>
+        <v>6506432</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>113470378</v>
       </c>
       <c r="B5" t="n">
-        <v>97370</v>
+        <v>97398</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113470429</v>
+        <v>113470423</v>
       </c>
       <c r="B6" t="n">
-        <v>78173</v>
+        <v>78201</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452529</v>
+        <v>452279</v>
       </c>
       <c r="R6" t="n">
-        <v>6506432</v>
+        <v>6506506</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113470427</v>
+        <v>113470421</v>
       </c>
       <c r="B7" t="n">
-        <v>78173</v>
+        <v>78201</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452388</v>
+        <v>452247</v>
       </c>
       <c r="R7" t="n">
-        <v>6506449</v>
+        <v>6506489</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113470425</v>
+        <v>113470377</v>
       </c>
       <c r="B8" t="n">
-        <v>78173</v>
+        <v>56826</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,34 +1303,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452327</v>
+        <v>452323</v>
       </c>
       <c r="R8" t="n">
-        <v>6506467</v>
+        <v>6506464</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113470376</v>
+        <v>113470427</v>
       </c>
       <c r="B9" t="n">
-        <v>97370</v>
+        <v>78201</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452378</v>
+        <v>452388</v>
       </c>
       <c r="R9" t="n">
-        <v>6506464</v>
+        <v>6506449</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113470377</v>
+        <v>113470376</v>
       </c>
       <c r="B10" t="n">
-        <v>56798</v>
+        <v>97398</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,40 +1508,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452323</v>
+        <v>452378</v>
       </c>
       <c r="R10" t="n">
         <v>6506464</v>

--- a/artfynd/A 45158-2023 artfynd.xlsx
+++ b/artfynd/A 45158-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113470425</v>
+        <v>113470427</v>
       </c>
       <c r="B2" t="n">
         <v>78201</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452327</v>
+        <v>452388</v>
       </c>
       <c r="R2" t="n">
-        <v>6506467</v>
+        <v>6506449</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113470431</v>
+        <v>113470425</v>
       </c>
       <c r="B3" t="n">
         <v>78201</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452564</v>
+        <v>452327</v>
       </c>
       <c r="R3" t="n">
-        <v>6506405</v>
+        <v>6506467</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113470429</v>
+        <v>113470431</v>
       </c>
       <c r="B4" t="n">
         <v>78201</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452529</v>
+        <v>452564</v>
       </c>
       <c r="R4" t="n">
-        <v>6506432</v>
+        <v>6506405</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113470378</v>
+        <v>113470377</v>
       </c>
       <c r="B5" t="n">
-        <v>97398</v>
+        <v>56826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452483</v>
+        <v>452323</v>
       </c>
       <c r="R5" t="n">
-        <v>6506438</v>
+        <v>6506464</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113470423</v>
+        <v>113470376</v>
       </c>
       <c r="B6" t="n">
-        <v>78201</v>
+        <v>97398</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452279</v>
+        <v>452378</v>
       </c>
       <c r="R6" t="n">
-        <v>6506506</v>
+        <v>6506464</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113470421</v>
+        <v>113470429</v>
       </c>
       <c r="B7" t="n">
         <v>78201</v>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452247</v>
+        <v>452529</v>
       </c>
       <c r="R7" t="n">
-        <v>6506489</v>
+        <v>6506432</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113470377</v>
+        <v>113470423</v>
       </c>
       <c r="B8" t="n">
-        <v>56826</v>
+        <v>78201</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,39 +1308,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452323</v>
+        <v>452279</v>
       </c>
       <c r="R8" t="n">
-        <v>6506464</v>
+        <v>6506506</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113470427</v>
+        <v>113470378</v>
       </c>
       <c r="B9" t="n">
-        <v>78201</v>
+        <v>97398</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452388</v>
+        <v>452483</v>
       </c>
       <c r="R9" t="n">
-        <v>6506449</v>
+        <v>6506438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113470376</v>
+        <v>113470421</v>
       </c>
       <c r="B10" t="n">
-        <v>97398</v>
+        <v>78201</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452378</v>
+        <v>452247</v>
       </c>
       <c r="R10" t="n">
-        <v>6506464</v>
+        <v>6506489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45158-2023 artfynd.xlsx
+++ b/artfynd/A 45158-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113470427</v>
+        <v>113470429</v>
       </c>
       <c r="B2" t="n">
         <v>78201</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452388</v>
+        <v>452529</v>
       </c>
       <c r="R2" t="n">
-        <v>6506449</v>
+        <v>6506432</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113470425</v>
+        <v>113470376</v>
       </c>
       <c r="B3" t="n">
-        <v>78201</v>
+        <v>97402</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452327</v>
+        <v>452378</v>
       </c>
       <c r="R3" t="n">
-        <v>6506467</v>
+        <v>6506464</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113470431</v>
+        <v>113470425</v>
       </c>
       <c r="B4" t="n">
         <v>78201</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452564</v>
+        <v>452327</v>
       </c>
       <c r="R4" t="n">
-        <v>6506405</v>
+        <v>6506467</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113470376</v>
+        <v>113470423</v>
       </c>
       <c r="B6" t="n">
-        <v>97398</v>
+        <v>78201</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452378</v>
+        <v>452279</v>
       </c>
       <c r="R6" t="n">
-        <v>6506464</v>
+        <v>6506506</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113470429</v>
+        <v>113470427</v>
       </c>
       <c r="B7" t="n">
         <v>78201</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452529</v>
+        <v>452388</v>
       </c>
       <c r="R7" t="n">
-        <v>6506432</v>
+        <v>6506449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113470423</v>
+        <v>113470421</v>
       </c>
       <c r="B8" t="n">
         <v>78201</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452279</v>
+        <v>452247</v>
       </c>
       <c r="R8" t="n">
-        <v>6506506</v>
+        <v>6506489</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113470378</v>
+        <v>113470431</v>
       </c>
       <c r="B9" t="n">
-        <v>97398</v>
+        <v>78201</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452483</v>
+        <v>452564</v>
       </c>
       <c r="R9" t="n">
-        <v>6506438</v>
+        <v>6506405</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113470421</v>
+        <v>113470378</v>
       </c>
       <c r="B10" t="n">
-        <v>78201</v>
+        <v>97402</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452247</v>
+        <v>452483</v>
       </c>
       <c r="R10" t="n">
-        <v>6506489</v>
+        <v>6506438</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45158-2023 artfynd.xlsx
+++ b/artfynd/A 45158-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113470429</v>
+        <v>113470376</v>
       </c>
       <c r="B2" t="n">
-        <v>78201</v>
+        <v>97402</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452529</v>
+        <v>452378</v>
       </c>
       <c r="R2" t="n">
-        <v>6506432</v>
+        <v>6506464</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113470376</v>
+        <v>113470425</v>
       </c>
       <c r="B3" t="n">
-        <v>97402</v>
+        <v>78201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452378</v>
+        <v>452327</v>
       </c>
       <c r="R3" t="n">
-        <v>6506464</v>
+        <v>6506467</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113470425</v>
+        <v>113470427</v>
       </c>
       <c r="B4" t="n">
         <v>78201</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452327</v>
+        <v>452388</v>
       </c>
       <c r="R4" t="n">
-        <v>6506467</v>
+        <v>6506449</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113470427</v>
+        <v>113470431</v>
       </c>
       <c r="B7" t="n">
         <v>78201</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452388</v>
+        <v>452564</v>
       </c>
       <c r="R7" t="n">
-        <v>6506449</v>
+        <v>6506405</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113470431</v>
+        <v>113470378</v>
       </c>
       <c r="B9" t="n">
-        <v>78201</v>
+        <v>97402</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452564</v>
+        <v>452483</v>
       </c>
       <c r="R9" t="n">
-        <v>6506405</v>
+        <v>6506438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113470378</v>
+        <v>113470429</v>
       </c>
       <c r="B10" t="n">
-        <v>97402</v>
+        <v>78201</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452483</v>
+        <v>452529</v>
       </c>
       <c r="R10" t="n">
-        <v>6506438</v>
+        <v>6506432</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45158-2023 artfynd.xlsx
+++ b/artfynd/A 45158-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113470376</v>
+        <v>113470378</v>
       </c>
       <c r="B2" t="n">
         <v>97402</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452378</v>
+        <v>452483</v>
       </c>
       <c r="R2" t="n">
-        <v>6506464</v>
+        <v>6506438</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113470425</v>
+        <v>113470429</v>
       </c>
       <c r="B3" t="n">
         <v>78201</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452327</v>
+        <v>452529</v>
       </c>
       <c r="R3" t="n">
-        <v>6506467</v>
+        <v>6506432</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113470427</v>
+        <v>113470421</v>
       </c>
       <c r="B4" t="n">
         <v>78201</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452388</v>
+        <v>452247</v>
       </c>
       <c r="R4" t="n">
-        <v>6506449</v>
+        <v>6506489</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113470377</v>
+        <v>113470423</v>
       </c>
       <c r="B5" t="n">
-        <v>56826</v>
+        <v>78201</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,39 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452323</v>
+        <v>452279</v>
       </c>
       <c r="R5" t="n">
-        <v>6506464</v>
+        <v>6506506</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113470423</v>
+        <v>113470427</v>
       </c>
       <c r="B6" t="n">
         <v>78201</v>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452279</v>
+        <v>452388</v>
       </c>
       <c r="R6" t="n">
-        <v>6506506</v>
+        <v>6506449</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113470431</v>
+        <v>113470376</v>
       </c>
       <c r="B7" t="n">
-        <v>78201</v>
+        <v>97402</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452564</v>
+        <v>452378</v>
       </c>
       <c r="R7" t="n">
-        <v>6506405</v>
+        <v>6506464</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113470421</v>
+        <v>113470431</v>
       </c>
       <c r="B8" t="n">
         <v>78201</v>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452247</v>
+        <v>452564</v>
       </c>
       <c r="R8" t="n">
-        <v>6506489</v>
+        <v>6506405</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113470378</v>
+        <v>113470377</v>
       </c>
       <c r="B9" t="n">
-        <v>97402</v>
+        <v>56826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,38 +1401,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452483</v>
+        <v>452323</v>
       </c>
       <c r="R9" t="n">
-        <v>6506438</v>
+        <v>6506464</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113470429</v>
+        <v>113470425</v>
       </c>
       <c r="B10" t="n">
         <v>78201</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452529</v>
+        <v>452327</v>
       </c>
       <c r="R10" t="n">
-        <v>6506432</v>
+        <v>6506467</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45158-2023 artfynd.xlsx
+++ b/artfynd/A 45158-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45158-2023 artfynd.xlsx
+++ b/artfynd/A 45158-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113470423</v>
+        <v>114384801</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452279</v>
+        <v>452522</v>
       </c>
       <c r="R2" t="n">
-        <v>6506506</v>
+        <v>6506437</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113470425</v>
+        <v>114384802</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452326</v>
+        <v>452310</v>
       </c>
       <c r="R3" t="n">
-        <v>6506467</v>
+        <v>6506439</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,50 +869,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113470376</v>
+        <v>113470377</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Haboskogen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452377</v>
+        <v>452323</v>
       </c>
       <c r="R4" t="n">
-        <v>6506465</v>
+        <v>6506464</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113470431</v>
+        <v>113470376</v>
       </c>
       <c r="B5" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452564</v>
+        <v>452377</v>
       </c>
       <c r="R5" t="n">
-        <v>6506405</v>
+        <v>6506465</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,12 +1071,7 @@
         <v>113470378</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,37 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113470421</v>
+        <v>113470345</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452247</v>
+        <v>452585</v>
       </c>
       <c r="R7" t="n">
-        <v>6506489</v>
+        <v>6506444</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,521 +1259,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>113470429</v>
-      </c>
-      <c r="B8" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Haboskogen, Vg</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>452530</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6506433</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Töreboda</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Töreboda</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Anna Sjövall</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Anna Sjövall</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>113470427</v>
-      </c>
-      <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Haboskogen, Vg</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>452388</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6506449</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Töreboda</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Töreboda</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Anna Sjövall</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Anna Sjövall</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>113470377</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Haboskogen, Vg</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>452323</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6506464</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Töreboda</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Töreboda</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Anna Sjövall</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Anna Sjövall</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>114384801</v>
-      </c>
-      <c r="B11" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Haboskogen, Vg</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>452522</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6506437</v>
-      </c>
-      <c r="S11" t="n">
-        <v>50</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Töreboda</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Töreboda</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Anna Sjövall</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Anna Sjövall</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>114384802</v>
-      </c>
-      <c r="B12" t="n">
-        <v>90954</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>6031</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Sparassis crispa</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Haboskogen, Vg</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>452310</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6506439</v>
-      </c>
-      <c r="S12" t="n">
-        <v>50</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Töreboda</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Töreboda</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Anna Sjövall</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Anna Sjövall</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
